--- a/product_selector_out/STM32F334 - diff.xlsx
+++ b/product_selector_out/STM32F334 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,6 +47,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
@@ -58,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18">
@@ -667,22 +667,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -694,70 +690,62 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F334C6</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F334C6</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -766,40 +754,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F334C6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10||9</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10, 9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -807,26 +799,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10||9 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -834,16 +826,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -853,63 +845,71 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>25 (workbook and API agree)</t>
+          <t>24||25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>24, 25</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>24||25 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -921,14 +921,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>24||25</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>10</t>
@@ -936,7 +932,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -948,70 +944,62 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>24, 25</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>24||25 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1020,21 +1008,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1043,88 +1031,76 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1138,7 +1114,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1147,7 +1123,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1161,7 +1137,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1170,25 +1146,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15||18</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -1197,25 +1173,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15, 18</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -1224,25 +1200,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>25 (workbook and API agree)</t>
+          <t>15||18 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -1251,53 +1227,61 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>37||38</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>37, 38</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1307,376 +1291,68 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>37||38 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32F334R8</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32F334R8</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>37 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>37||38</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>37, 38</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>37||38 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E58"/>
+  <autoFilter ref="A18:E46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F334 - diff.xlsx
+++ b/product_selector_out/STM32F334 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="18">
@@ -759,22 +759,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>10||9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -786,137 +782,117 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>10, 9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>10||9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>24||25</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>24, 25</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>24||25 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -939,7 +915,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -962,7 +938,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -985,7 +961,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1008,138 +984,162 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15||18</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15, 18</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>A/D Converters 12-bit | Number of Channels typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>15||18 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>37||38</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>37, 38</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>37||38 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1151,22 +1151,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>15||18</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1178,181 +1174,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>15, 18</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>A/D Converters 12-bit | Number of Channels typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>15||18 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>37||38</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>37, 38</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>37||38 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E46"/>
+  <autoFilter ref="A18:E40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F334 - diff.xlsx
+++ b/product_selector_out/STM32F334 - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="18">
